--- a/tests/coil_3D_avoltemf_timint/input_template.xlsx
+++ b/tests/coil_3D_avoltemf_timint/input_template.xlsx
@@ -980,7 +980,7 @@
         <v>20</v>
       </c>
       <c r="K2" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L2" s="3">
         <v>0</v>
